--- a/task150/golden/classroom_placement_2028-33.xlsx
+++ b/task150/golden/classroom_placement_2028-33.xlsx
@@ -1323,10 +1323,10 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" ht="64" customHeight="1">
+    <row r="13" ht="92" customHeight="1">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>One class for each room and session in use on October 1: a combination class's grade sections and a co-taught class's two sections count once, a half-day kindergarten's morning and afternoon classes twice. Homeroom sections (HR-K to HR-5) running on October 1 with at least one pupil enrolled that day (sections_fall2026.csv, section_enrollment_fall2026.csv).</t>
+          <t>The district's class count (sis_export_notes.txt): one class for each room and session among the homeroom sections (HR-K to HR-5) open on October 1 with at least one pupil enrolled that day, in the grade of its pupils on the October 1 count. A combination class's grade sections and a co-taught class's two sections count once, a half-day kindergarten's morning and afternoon classes twice, and the classes opened in September on spare sections count in their pupils' grade, not the section's course (sections_fall2026.csv, section_enrollment_fall2026.csv, october_membership_2019-2026.csv).</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,7 @@
     <row r="10" ht="78" customHeight="1">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Children: each child once (state ID), from the registration platform's enrollments open on October 1 (preschool_enrollments_2026-27.csv) and the special education roster's children placed in the school's special education and inclusive preschool classrooms (ecse_roster_2026-10-01.xlsx); children served itinerantly are not in a class. Classrooms: the rooms those classes meet in, morning and afternoon classes in one room counted once.</t>
+          <t>Children: each child once (state ID), from the registration platform's enrollments open on October 1 (preschool_enrollments_2026-27.csv) and the special education roster's children whose class meets at the school, by the roster's classroom rather than its case school (ecse_roster_2026-10-01.xlsx); children served itinerantly are not in a class. Classrooms: the rooms those classes meet in, morning and afternoon classes in one room counted once.</t>
         </is>
       </c>
     </row>
